--- a/diseases/d039/1995-1999.xlsx
+++ b/diseases/d039/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>4</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>3</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>2</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>1</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>2</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>4</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>1</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>3</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>1</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>4</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>3</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14520,9 +14415,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14913,9 +14805,6 @@
       <c r="O74" t="n">
         <v>2</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15306,9 +15195,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15699,9 +15585,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16092,9 +15975,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16485,9 +16365,6 @@
       <c r="O82" t="n">
         <v>4</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16878,9 +16755,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17271,9 +17145,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17664,9 +17535,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18057,9 +17925,6 @@
       <c r="O90" t="n">
         <v>1</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18450,9 +18315,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18843,9 +18705,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19236,9 +19095,6 @@
       <c r="O96" t="n">
         <v>2</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19774,9 +19630,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="S99" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20398,9 +20251,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="S102" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20791,9 +20641,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21560,9 +21407,6 @@
       <c r="O108" t="n">
         <v>1</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="S108" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21953,9 +21797,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="S110" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22722,9 +22563,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="S114" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23115,9 +22953,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="S116" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23884,9 +23719,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="S120" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24277,9 +24109,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="S122" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25046,9 +24875,6 @@
       <c r="O126" t="n">
         <v>1</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="S126" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25439,9 +25265,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="S128" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26208,9 +26031,6 @@
       <c r="O132" t="n">
         <v>1</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="S132" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26601,9 +26421,6 @@
       <c r="O134" t="n">
         <v>1</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27370,9 +27187,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="S138" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27763,9 +27577,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="S140" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28532,9 +28343,6 @@
       <c r="O144" t="n">
         <v>1</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="S144" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28925,9 +28733,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="S146" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29694,9 +29499,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="S150" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30087,9 +29889,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="S152" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30856,9 +30655,6 @@
       <c r="O156" t="n">
         <v>1</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="S156" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31249,9 +31045,6 @@
       <c r="O158" t="n">
         <v>1</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="S158" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32018,9 +31811,6 @@
       <c r="O162" t="n">
         <v>1</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="S162" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32411,9 +32201,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="S164" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33180,9 +32967,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="S168" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33573,9 +33357,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="S170" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34111,9 +33892,6 @@
       <c r="O173" t="n">
         <v>12</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="S173" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34735,9 +34513,6 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="S176" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35128,9 +34903,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="S178" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35897,9 +35669,6 @@
       <c r="O182" t="n">
         <v>0</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="S182" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36290,9 +36059,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="S184" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37059,9 +36825,6 @@
       <c r="O188" t="n">
         <v>1</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="S188" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37452,9 +37215,6 @@
       <c r="O190" t="n">
         <v>1</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="S190" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38221,9 +37981,6 @@
       <c r="O194" t="n">
         <v>1</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="S194" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38614,9 +38371,6 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="S196" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39383,9 +39137,6 @@
       <c r="O200" t="n">
         <v>2</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="S200" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39776,9 +39527,6 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="S202" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40545,9 +40293,6 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="S206" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40938,9 +40683,6 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="S208" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41707,9 +41449,6 @@
       <c r="O212" t="n">
         <v>3</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="S212" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42100,9 +41839,6 @@
       <c r="O214" t="n">
         <v>0</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="S214" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42869,9 +42605,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="S218" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43262,9 +42995,6 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="S220" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44031,9 +43761,6 @@
       <c r="O224" t="n">
         <v>2</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="S224" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44424,9 +44151,6 @@
       <c r="O226" t="n">
         <v>0</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="S226" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45193,9 +44917,6 @@
       <c r="O230" t="n">
         <v>0</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="S230" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45586,9 +45307,6 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="S232" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46355,9 +46073,6 @@
       <c r="O236" t="n">
         <v>0</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="S236" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46748,9 +46463,6 @@
       <c r="O238" t="n">
         <v>0</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="S238" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47517,9 +47229,6 @@
       <c r="O242" t="n">
         <v>0</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="S242" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47910,9 +47619,6 @@
       <c r="O244" t="n">
         <v>0</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="S244" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48448,9 +48154,6 @@
       <c r="O247" t="n">
         <v>44</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="S247" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49072,9 +48775,6 @@
       <c r="O250" t="n">
         <v>0</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="S250" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49465,9 +49165,6 @@
       <c r="O252" t="n">
         <v>0</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="S252" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50234,9 +49931,6 @@
       <c r="O256" t="n">
         <v>0</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="S256" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50627,9 +50321,6 @@
       <c r="O258" t="n">
         <v>0</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="S258" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51396,9 +51087,6 @@
       <c r="O262" t="n">
         <v>0</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="S262" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51789,9 +51477,6 @@
       <c r="O264" t="n">
         <v>0</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="S264" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -52558,9 +52243,6 @@
       <c r="O268" t="n">
         <v>0</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="S268" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -52951,9 +52633,6 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="S270" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -53720,9 +53399,6 @@
       <c r="O274" t="n">
         <v>0</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="S274" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -54113,9 +53789,6 @@
       <c r="O276" t="n">
         <v>0</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="S276" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -54882,9 +54555,6 @@
       <c r="O280" t="n">
         <v>1</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="S280" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -55275,9 +54945,6 @@
       <c r="O282" t="n">
         <v>0</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="S282" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -56044,9 +55711,6 @@
       <c r="O286" t="n">
         <v>0</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="S286" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -56437,9 +56101,6 @@
       <c r="O288" t="n">
         <v>0</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="S288" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -57206,9 +56867,6 @@
       <c r="O292" t="n">
         <v>1</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="S292" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -57599,9 +57257,6 @@
       <c r="O294" t="n">
         <v>0</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="S294" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -58368,9 +58023,6 @@
       <c r="O298" t="n">
         <v>1</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="S298" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -58761,9 +58413,6 @@
       <c r="O300" t="n">
         <v>0</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="S300" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -59530,9 +59179,6 @@
       <c r="O304" t="n">
         <v>2</v>
       </c>
-      <c r="Q304" t="n">
-        <v>0</v>
-      </c>
       <c r="S304" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -59923,9 +59569,6 @@
       <c r="O306" t="n">
         <v>1</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="S306" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -60692,9 +60335,6 @@
       <c r="O310" t="n">
         <v>0</v>
       </c>
-      <c r="Q310" t="n">
-        <v>0</v>
-      </c>
       <c r="S310" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -61085,9 +60725,6 @@
       <c r="O312" t="n">
         <v>0</v>
       </c>
-      <c r="Q312" t="n">
-        <v>0</v>
-      </c>
       <c r="S312" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -61852,9 +61489,6 @@
         <v>0</v>
       </c>
       <c r="O316" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q316" t="n">
         <v>0</v>
       </c>
       <c r="S316" t="inlineStr">
